--- a/LAB2.xlsx
+++ b/LAB2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\Y4k2_tester\lab 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E256B20-CE5E-4D5E-9A27-260F1392BF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D67A096-ABD4-4F61-881E-EB28DC5B9E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bài 1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="251">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -48,9 +48,6 @@
     <t>Reviewed By</t>
   </si>
   <si>
-    <t>Bill</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
@@ -69,9 +66,6 @@
     <t>Date Tested</t>
   </si>
   <si>
-    <t>1-Jan-2023</t>
-  </si>
-  <si>
     <t>Test Case (Pass/Fail/Not Executed)</t>
   </si>
   <si>
@@ -219,9 +213,6 @@
     <t>Bài 2 - Nhập dãy số (độ dài 6-10 ký tự)</t>
   </si>
   <si>
-    <t>Thiết kế test case theo kỹ thuật phân vùng tương đương - Bài 2.</t>
-  </si>
-  <si>
     <t>Có ô input chỉ cho nhập dãy số</t>
   </si>
   <si>
@@ -264,24 +255,15 @@
     <t>Báo lỗi độ dài</t>
   </si>
   <si>
-    <t>Biên dưới hợp lệ</t>
-  </si>
-  <si>
     <t>Input = 123456</t>
   </si>
   <si>
     <t>Chấp nhận</t>
   </si>
   <si>
-    <t>Giữa vùng hợp lệ</t>
-  </si>
-  <si>
     <t>Input = 1234567</t>
   </si>
   <si>
-    <t>Biên trên hợp lệ</t>
-  </si>
-  <si>
     <t>Input = 1234567890</t>
   </si>
   <si>
@@ -790,6 +772,18 @@
   </si>
   <si>
     <t>Huynh</t>
+  </si>
+  <si>
+    <t>Thiết kế test case nhập dãy số 6–10 ký tự - Bài 2.</t>
+  </si>
+  <si>
+    <t>Biên dưới hợp lệ =6</t>
+  </si>
+  <si>
+    <t>Giữa vùng hợp lệ &gt;6 và &lt;10</t>
+  </si>
+  <si>
+    <t>Biên trên hợp lệ =10</t>
   </si>
 </sst>
 </file>
@@ -872,7 +866,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -898,28 +892,31 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1240,241 +1237,241 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
+      <c r="B2" s="16"/>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="E2" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
       <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="15">
+        <v>5</v>
+      </c>
+      <c r="I2" s="14">
         <v>2.1</v>
       </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" t="s">
-        <v>249</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="E6" s="17">
         <v>46174</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+        <v>11</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>3</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="3">
         <v>3</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>4</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="3">
         <v>4</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D15" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D18" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -1482,20 +1479,20 @@
     </row>
     <row r="21" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
@@ -1503,20 +1500,20 @@
     </row>
     <row r="22" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
@@ -1524,20 +1521,20 @@
     </row>
     <row r="23" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
@@ -1545,20 +1542,20 @@
     </row>
     <row r="24" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
@@ -1566,20 +1563,20 @@
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
@@ -1587,45 +1584,45 @@
     </row>
     <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="14"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="14"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1633,6 +1630,20 @@
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="B8:G8"/>
     <mergeCell ref="H27:K27"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="I11:K11"/>
@@ -1641,23 +1652,9 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="I8:K8"/>
     <mergeCell ref="H26:K26"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="I10:K10"/>
     <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B8:G8"/>
     <mergeCell ref="I12:K12"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1682,392 +1679,391 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="E1" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
+      <c r="B2" s="16"/>
       <c r="C2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
+      <c r="E2" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
       <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:11" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" t="s">
-        <v>249</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="E6" s="17">
         <v>46174</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+        <v>11</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>3</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="3">
         <v>3</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>4</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="3">
         <v>4</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D15" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D16" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D18" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="11"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="11"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="11"/>
     </row>
     <row r="24" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="14"/>
+        <v>46</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="11"/>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="11"/>
     </row>
     <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="14"/>
+        <v>52</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="11"/>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="14"/>
+        <v>55</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="11"/>
     </row>
     <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2075,6 +2071,33 @@
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="H26:K26"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E26:G26"/>
     <mergeCell ref="E25:G25"/>
     <mergeCell ref="H27:K27"/>
     <mergeCell ref="B20:D20"/>
@@ -2091,33 +2114,6 @@
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="H25:K25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="H26:K26"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E26:G26"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2135,186 +2131,192 @@
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="8" max="8" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="E1" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="17">
+        <v>46174</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>3</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="3">
         <v>3</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>4</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="3">
         <v>4</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2322,249 +2324,279 @@
     <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D29" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D30" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D31" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="11"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="11"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="11"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="14"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="11"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="11"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="14"/>
+        <v>52</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="11"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="14"/>
+        <v>55</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="11"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="14"/>
+        <v>113</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="46">
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="E34:G34"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="E33:G33"/>
     <mergeCell ref="E39:G39"/>
@@ -2581,36 +2613,6 @@
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="H35:K35"/>
     <mergeCell ref="I8:K8"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B9:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2628,186 +2630,192 @@
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="8" max="8" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="E1" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="17">
+        <v>46174</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>3</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="3">
         <v>3</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>4</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="3">
         <v>4</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2815,291 +2823,327 @@
     <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D30" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D31" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="11"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="11"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="11"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="14"/>
+      <c r="B36" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="11"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="11"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="14"/>
+        <v>52</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="11"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="14"/>
+        <v>55</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="11"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="14"/>
+        <v>113</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="11"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="14"/>
+        <v>147</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="11"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="14"/>
+        <v>150</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="H42:K42"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="I6:K6"/>
     <mergeCell ref="H36:K36"/>
     <mergeCell ref="I11:K11"/>
@@ -3116,42 +3160,6 @@
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="E37:G37"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="H42:K42"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H40:K40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3169,186 +3177,192 @@
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="8" max="8" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="E1" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="17">
+        <v>46174</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>3</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="3">
         <v>3</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>4</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="3">
         <v>4</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3356,228 +3370,255 @@
     <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D29" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D30" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D31" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="11"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="11"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="11"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="14"/>
+        <v>46</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="11"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="11"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="14"/>
+        <v>52</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="11"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="14"/>
+        <v>55</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="H33:K33"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E32:G32"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E38:G38"/>
     <mergeCell ref="E37:G37"/>
     <mergeCell ref="H39:K39"/>
     <mergeCell ref="B32:D32"/>
@@ -3594,33 +3635,6 @@
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="H37:K37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E32:G32"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="H33:K33"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I2:K2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3637,187 +3651,193 @@
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" customWidth="1"/>
+    <col min="8" max="8" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="E1" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="17">
+        <v>46174</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>3</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="3">
         <v>3</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>4</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="3">
         <v>4</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3825,276 +3845,293 @@
     <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D29" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D30" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D31" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="11"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="11"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="11"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="14"/>
+        <v>46</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="11"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="11"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="14"/>
+        <v>52</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="11"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="14"/>
+        <v>55</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="11"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="14"/>
+        <v>113</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="11"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="14"/>
+        <v>147</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E40:G40"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="E32:G32"/>
@@ -4106,38 +4143,21 @@
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="E33:G33"/>
-    <mergeCell ref="H35:K35"/>
     <mergeCell ref="I8:K8"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="E39:G39"/>
     <mergeCell ref="B8:G8"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E40:G40"/>
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H33:K33"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E34:G34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4154,187 +4174,193 @@
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" customWidth="1"/>
+    <col min="8" max="8" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="16"/>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="E1" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
+        <v>7</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="17">
+        <v>46174</v>
+      </c>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
     </row>
     <row r="7" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
     </row>
     <row r="9" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
+      <c r="B9" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
     </row>
     <row r="10" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
+      <c r="B10" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="3">
         <v>2</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
+      <c r="I10" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
     </row>
     <row r="11" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>3</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="3">
         <v>3</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
     </row>
     <row r="12" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>4</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="3">
         <v>4</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
     </row>
     <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -4342,276 +4368,293 @@
     <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D26" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D29" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D30" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="D31" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="11"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="14"/>
+        <v>38</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="11"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="14"/>
+        <v>42</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="11"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="F36" s="11"/>
-      <c r="G36" s="11"/>
-      <c r="H36" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="14"/>
+        <v>46</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="11"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="14"/>
+        <v>48</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="11"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="14"/>
+        <v>52</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="11"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="10" t="s">
-        <v>242</v>
-      </c>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
-      <c r="H39" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="14"/>
+        <v>55</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="11"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="I40" s="11"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="14"/>
+        <v>113</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="11"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="14"/>
+        <v>147</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="E35:G35"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="H32:K32"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="E36:G36"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="H38:K38"/>
+    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="H40:K40"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="H39:K39"/>
+    <mergeCell ref="H36:K36"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E40:G40"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="E32:G32"/>
@@ -4623,38 +4666,21 @@
     <mergeCell ref="I11:K11"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="E33:G33"/>
-    <mergeCell ref="H35:K35"/>
     <mergeCell ref="I8:K8"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="H38:K38"/>
-    <mergeCell ref="H41:K41"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E38:G38"/>
-    <mergeCell ref="H40:K40"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="H39:K39"/>
-    <mergeCell ref="H34:K34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="H36:K36"/>
-    <mergeCell ref="E39:G39"/>
     <mergeCell ref="B8:G8"/>
-    <mergeCell ref="E34:G34"/>
-    <mergeCell ref="E40:G40"/>
     <mergeCell ref="I12:K12"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H33:K33"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="E36:G36"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="H32:K32"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="H37:K37"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="H34:K34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E34:G34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
